--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/alexandra_veizu_uipath_com/Documents/Documents/Projects/REFrameworkNET5/StudioTemplates/REFramework/contentFiles/any/any/pt2/VisualBasic/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a98318606382685/Desktop/My Automations/ID Card Automation/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C54E24-BA5C-4BF9-8DAB-2778512EC11B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3A8A073-B91E-45B8-9DDF-ABC29DEB82BB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5556" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>Name</t>
   </si>
@@ -160,6 +160,51 @@
   </si>
   <si>
     <t>ProcessABCQueue</t>
+  </si>
+  <si>
+    <t>C:\Users\91905\OneDrive\Desktop\My Automations\ID Card Automation\Business\Data.xlsx</t>
+  </si>
+  <si>
+    <t>employees data which is stored in an Excel Sheet</t>
+  </si>
+  <si>
+    <t>Emp_Data</t>
+  </si>
+  <si>
+    <t>CardData</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>C:\Users\91905\OneDrive\Desktop\My Automations\ID Card Automation\Business\Images\</t>
+  </si>
+  <si>
+    <t>ImagePath</t>
+  </si>
+  <si>
+    <t>C:\Users\91905\OneDrive\Desktop\My Automations\ID Card Automation\Business\IdForm.docx</t>
+  </si>
+  <si>
+    <t>IdCardTemplate</t>
+  </si>
+  <si>
+    <t>A word Template to create Id Cards</t>
+  </si>
+  <si>
+    <t>IdCards</t>
+  </si>
+  <si>
+    <t>Final output of pdf of Id Cards</t>
+  </si>
+  <si>
+    <t>C:\Users\91905\OneDrive\Desktop\My Automations\ID Card Automation\Business\ID cards\</t>
   </si>
 </sst>
 </file>
@@ -212,10 +257,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -236,6 +281,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,7 +588,7 @@
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5546875" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="81.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.44140625" customWidth="1"/>
     <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
@@ -611,32 +660,83 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
